--- a/Configs/GameConfig/Datas/__tables__.xlsx
+++ b/Configs/GameConfig/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -119,15 +119,6 @@
     <t>界面UI.xlsx</t>
   </si>
   <si>
-    <t>Character.TbCharacterConfig</t>
-  </si>
-  <si>
-    <t>CharacterConfig</t>
-  </si>
-  <si>
-    <t>角色.xlsx</t>
-  </si>
-  <si>
     <t>Entity.TbEntityConfig</t>
   </si>
   <si>
@@ -135,15 +126,6 @@
   </si>
   <si>
     <t>实体.xlsx</t>
-  </si>
-  <si>
-    <t>Level.TbLevelConfig</t>
-  </si>
-  <si>
-    <t>LevelConfig</t>
-  </si>
-  <si>
-    <t>关卡.xlsx</t>
   </si>
 </sst>
 </file>
@@ -309,7 +291,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -319,6 +301,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -635,7 +623,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -659,16 +647,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -680,93 +668,99 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="22" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="22" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="22" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1088,8 +1082,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
   <cols>
     <col min="2" max="2" width="20.3833333333333" customWidth="1"/>
     <col min="3" max="3" width="15.575" customWidth="1"/>
@@ -1189,59 +1183,31 @@
       </c>
     </row>
     <row r="4" s="2" customFormat="1" spans="1:11">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
-      <c r="B5" t="s">
+    <row r="5" s="3" customFormat="1" spans="1:11">
+      <c r="B5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D5" t="b">
+      <c r="D5" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="3" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="B6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="B7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
